--- a/pensum/ok10/OK10_Investeringsanalyse_Regneark_Investering.xlsx
+++ b/pensum/ok10/OK10_Investeringsanalyse_Regneark_Investering.xlsx
@@ -1036,7 +1036,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1183,6 +1183,14 @@
     </xf>
     <xf numFmtId="167" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1506,7 +1514,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="24.75" customHeight="true" r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
@@ -1950,8 +1958,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="19" t="s">
+    <row ht="27" customHeight="true" r="36" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="37" r="A36" t="s">
         <v>87</v>
       </c>
       <c r="B36" s="21" t="s">
@@ -2751,8 +2759,8 @@
         <v>OK — levetiden får plass i tabellen</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="19" t="s">
+    <row ht="27" customHeight="true" r="41" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="37" r="A41" t="s">
         <v>157</v>
       </c>
       <c r="B41" s="33" t="str">
@@ -3207,8 +3215,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
+    <row ht="27" customHeight="true" r="31" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="37" r="A31" t="s">
         <v>189</v>
       </c>
       <c r="B31" s="33" t="str">
@@ -3216,8 +3224,8 @@
         <v>OK — høyere krav gir lavere nåverdi, hele tabellen igjennom</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
+    <row ht="27" customHeight="true" r="32" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="37" r="A32" t="s">
         <v>190</v>
       </c>
       <c r="B32" s="33" t="str">
@@ -3225,8 +3233,8 @@
         <v>OK — nåverdien skifter fortegn inne i tabellen, og der ligger internrenten</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
+    <row ht="39.75" customHeight="true" r="33" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="37" r="A33" t="s">
         <v>191</v>
       </c>
       <c r="B33" s="33" t="str">
@@ -3294,7 +3302,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="52.5" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22"/>
       <c r="B5" s="22" t="s">
         <v>196</v>
@@ -3553,8 +3561,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="21" t="s">
+    <row ht="27" customHeight="true" r="31" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="38" r="A31" t="s">
         <v>219</v>
       </c>
       <c r="B31" s="24" t="n">
